--- a/Outputs/Scenarios/PtX_demand_NL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_NL_Electrification.xlsx
@@ -498,7 +498,7 @@
         <v>0.007780804891708162</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05047885156377292</v>
+        <v>0.05047885156377293</v>
       </c>
       <c r="E2" t="n">
         <v>0.0005869991914447608</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01553277004395702</v>
+        <v>0.01553277004395703</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04109300256402444</v>
+        <v>0.04109300256402445</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0.001994653943655183</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08604906907805233</v>
+        <v>0.08604906907805232</v>
       </c>
     </row>
     <row r="31">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08604906907805233</v>
+        <v>0.08604906907805232</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_NL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_NL_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001347394788327499</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01473781155198666</v>
+        <v>0.01762961379460802</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00245630192533111</v>
+        <v>0.0030600240381304</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009825207701324438</v>
+        <v>0.0122400961525216</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01473781155198666</v>
+        <v>0.0122400961525216</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001079804696132394</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0211961716583428</v>
+        <v>0.02080949938659654</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0006536060097405225</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1989714581857928</v>
+        <v>0.195341710937587</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.941367814293906e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00245630192533111</v>
+        <v>0.0030600240381304</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001994653943655183</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08604906907805232</v>
+        <v>0.09436137934598621</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01434151151300872</v>
+        <v>0.01637858278881709</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05736604605203489</v>
+        <v>0.06551433115526835</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08604906907805232</v>
+        <v>0.06551433115526835</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001049817865081676</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01434151151300872</v>
+        <v>0.01637858278881709</v>
       </c>
     </row>
     <row r="43">
